--- a/outputs/Block2_National_Nested_Folds_v12.xlsx
+++ b/outputs/Block2_National_Nested_Folds_v12.xlsx
@@ -528,13 +528,13 @@
         <v>3.967840869181249</v>
       </c>
       <c r="G2">
-        <v>6.319648917692146</v>
+        <v>6.31964891769215</v>
       </c>
       <c r="H2">
-        <v>0.5024446975396469</v>
+        <v>0.5024446975396468</v>
       </c>
       <c r="I2">
-        <v>0.497555302460353</v>
+        <v>0.4975553024603532</v>
       </c>
       <c r="J2" t="s">
         <v>21</v>
@@ -660,13 +660,13 @@
         <v>5.114197416147853</v>
       </c>
       <c r="G5">
-        <v>6.2966103261324</v>
+        <v>6.296610326132406</v>
       </c>
       <c r="H5">
-        <v>0.5542790760933822</v>
+        <v>0.554279076093382</v>
       </c>
       <c r="I5">
-        <v>0.4457209239066178</v>
+        <v>0.4457209239066179</v>
       </c>
       <c r="J5" t="s">
         <v>21</v>
@@ -792,13 +792,13 @@
         <v>3.69459999331273</v>
       </c>
       <c r="G8">
-        <v>6.282988749273805</v>
+        <v>6.282988749273807</v>
       </c>
       <c r="H8">
-        <v>0.5705583655149384</v>
+        <v>0.5705583655149382</v>
       </c>
       <c r="I8">
-        <v>0.4294416344850616</v>
+        <v>0.4294416344850617</v>
       </c>
       <c r="J8" t="s">
         <v>21</v>
@@ -924,10 +924,10 @@
         <v>4.139788819212143</v>
       </c>
       <c r="G11">
-        <v>5.291968212462608</v>
+        <v>5.291968212462604</v>
       </c>
       <c r="H11">
-        <v>0.5074764797709387</v>
+        <v>0.5074764797709386</v>
       </c>
       <c r="I11">
         <v>0.4925235202290613</v>
@@ -1056,13 +1056,13 @@
         <v>3.753336425842188</v>
       </c>
       <c r="G14">
-        <v>6.661208146972521</v>
+        <v>6.661208146972516</v>
       </c>
       <c r="H14">
-        <v>0.5677908010583419</v>
+        <v>0.5677908010583421</v>
       </c>
       <c r="I14">
-        <v>0.4322091989416581</v>
+        <v>0.4322091989416579</v>
       </c>
       <c r="J14" t="s">
         <v>21</v>

--- a/outputs/Block2_National_Nested_Folds_v12.xlsx
+++ b/outputs/Block2_National_Nested_Folds_v12.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="23">
   <si>
     <t>Outer Test Year</t>
   </si>
@@ -67,18 +67,9 @@
     <t>Popular Vote</t>
   </si>
   <si>
-    <t>House Buckets</t>
-  </si>
-  <si>
-    <t>Senate Buckets</t>
-  </si>
-  <si>
     <t>ExpectedVoteAnchor</t>
   </si>
   <si>
-    <t>Ridge</t>
-  </si>
-  <si>
     <t>max_depth=3; max_features=0.5; min_samples_leaf=1</t>
   </si>
   <si>
@@ -91,13 +82,7 @@
     <t>alpha=10.0; solver=lsqr</t>
   </si>
   <si>
-    <t>alpha=100.0; solver=lsqr</t>
-  </si>
-  <si>
     <t>D-R popular vote margin MAE (percentage points)</t>
-  </si>
-  <si>
-    <t>Mean target MAE in native units</t>
   </si>
 </sst>
 </file>
@@ -455,7 +440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P16"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -516,7 +501,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D2">
         <v>0.02029126213592225</v>
@@ -525,28 +510,28 @@
         <v>6.833333333333337</v>
       </c>
       <c r="F2">
-        <v>3.967840869181249</v>
+        <v>5.024892949502592</v>
       </c>
       <c r="G2">
-        <v>6.31964891769215</v>
+        <v>6.293341500897182</v>
       </c>
       <c r="H2">
-        <v>0.5024446975396468</v>
+        <v>0.4795622463099145</v>
       </c>
       <c r="I2">
-        <v>0.4975553024603532</v>
+        <v>0.5204377536900855</v>
       </c>
       <c r="J2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="M2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="N2">
         <v>1.81108860322371</v>
@@ -560,131 +545,149 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3">
-        <v>2006</v>
+        <v>2010</v>
       </c>
       <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
         <v>17</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3">
+        <v>0.0156565217391304</v>
+      </c>
+      <c r="E3">
+        <v>8.33333333333333</v>
+      </c>
+      <c r="F3">
+        <v>5.511329271180229</v>
+      </c>
+      <c r="G3">
+        <v>6.000052338103545</v>
+      </c>
+      <c r="H3">
+        <v>0.5625189673269325</v>
+      </c>
+      <c r="I3">
+        <v>0.4374810326730675</v>
+      </c>
+      <c r="J3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" t="s">
         <v>20</v>
       </c>
-      <c r="D3">
-        <v>2.551785240009931</v>
-      </c>
-      <c r="E3">
-        <v>7.239583333333334</v>
-      </c>
-      <c r="F3">
-        <v>6.48365908322933</v>
-      </c>
-      <c r="G3">
-        <v>7.074413203214709</v>
-      </c>
-      <c r="H3">
-        <v>0.5018369690008886</v>
-      </c>
-      <c r="I3">
-        <v>0.4981630309991115</v>
-      </c>
-      <c r="J3" t="s">
+      <c r="M3" t="s">
         <v>22</v>
       </c>
-      <c r="K3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L3" t="s">
-        <v>24</v>
-      </c>
-      <c r="M3" t="s">
-        <v>27</v>
+      <c r="N3">
+        <v>2.043919732157621</v>
+      </c>
+      <c r="O3">
+        <v>2.043919732157621</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4">
-        <v>2006</v>
+        <v>2014</v>
       </c>
       <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4">
+        <v>0.01536824324324321</v>
+      </c>
+      <c r="E4">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="F4">
+        <v>4.938432989723164</v>
+      </c>
+      <c r="G4">
+        <v>5.199541323754511</v>
+      </c>
+      <c r="H4">
+        <v>0.6207814507798668</v>
+      </c>
+      <c r="I4">
+        <v>0.3792185492201333</v>
+      </c>
+      <c r="J4" t="s">
         <v>18</v>
       </c>
-      <c r="C4" t="s">
+      <c r="K4" t="s">
+        <v>19</v>
+      </c>
+      <c r="L4" t="s">
         <v>20</v>
       </c>
-      <c r="D4">
-        <v>0.9615308633365063</v>
-      </c>
-      <c r="E4">
-        <v>1.229166666666667</v>
-      </c>
-      <c r="F4">
-        <v>1.132854998160983</v>
-      </c>
-      <c r="G4">
-        <v>1.206864525428687</v>
-      </c>
-      <c r="H4">
-        <v>0.4944540683139197</v>
-      </c>
-      <c r="I4">
-        <v>0.5055459316860803</v>
-      </c>
-      <c r="J4" t="s">
+      <c r="M4" t="s">
         <v>22</v>
       </c>
-      <c r="K4" t="s">
-        <v>22</v>
-      </c>
-      <c r="L4" t="s">
-        <v>24</v>
-      </c>
-      <c r="M4" t="s">
-        <v>27</v>
+      <c r="N4">
+        <v>2.063735477916174</v>
+      </c>
+      <c r="O4">
+        <v>2.063735477916174</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:16">
       <c r="A5">
-        <v>2010</v>
+        <v>2018</v>
       </c>
       <c r="B5" t="s">
         <v>16</v>
       </c>
       <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5">
+        <v>0.006999999999999978</v>
+      </c>
+      <c r="E5">
+        <v>6.533333333333332</v>
+      </c>
+      <c r="F5">
+        <v>5.118421138250199</v>
+      </c>
+      <c r="G5">
+        <v>5.647888599724915</v>
+      </c>
+      <c r="H5">
+        <v>0.4820351620929062</v>
+      </c>
+      <c r="I5">
+        <v>0.5179648379070939</v>
+      </c>
+      <c r="J5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K5" t="s">
         <v>19</v>
       </c>
-      <c r="D5">
-        <v>0.0156565217391304</v>
-      </c>
-      <c r="E5">
-        <v>8.33333333333333</v>
-      </c>
-      <c r="F5">
-        <v>5.114197416147853</v>
-      </c>
-      <c r="G5">
-        <v>6.296610326132406</v>
-      </c>
-      <c r="H5">
-        <v>0.554279076093382</v>
-      </c>
-      <c r="I5">
-        <v>0.4457209239066179</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="L5" t="s">
         <v>21</v>
       </c>
-      <c r="K5" t="s">
+      <c r="M5" t="s">
         <v>22</v>
       </c>
-      <c r="L5" t="s">
-        <v>23</v>
-      </c>
-      <c r="M5" t="s">
-        <v>26</v>
-      </c>
       <c r="N5">
-        <v>2.043919732157621</v>
+        <v>2.578312672275927</v>
       </c>
       <c r="O5">
-        <v>2.043919732157621</v>
+        <v>2.578312672275927</v>
       </c>
       <c r="P5">
         <v>0</v>
@@ -692,480 +695,52 @@
     </row>
     <row r="6" spans="1:16">
       <c r="A6">
-        <v>2010</v>
+        <v>2022</v>
       </c>
       <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
         <v>17</v>
       </c>
-      <c r="C6" t="s">
-        <v>20</v>
-      </c>
       <c r="D6">
-        <v>7.349523097808222</v>
+        <v>0.001374999999999932</v>
       </c>
       <c r="E6">
-        <v>5.635416666666666</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F6">
-        <v>4.452517519892867</v>
+        <v>6.513385977378117</v>
       </c>
       <c r="G6">
-        <v>5.027182834901101</v>
+        <v>6.165678152352301</v>
       </c>
       <c r="H6">
-        <v>0.5255808205584616</v>
+        <v>0.5964553373998983</v>
       </c>
       <c r="I6">
-        <v>0.4744191794415384</v>
+        <v>0.4035446626001017</v>
       </c>
       <c r="J6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L6" t="s">
         <v>21</v>
       </c>
-      <c r="K6" t="s">
+      <c r="M6" t="s">
         <v>22</v>
       </c>
-      <c r="L6" t="s">
-        <v>23</v>
-      </c>
-      <c r="M6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16">
-      <c r="A7">
-        <v>2010</v>
-      </c>
-      <c r="B7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7">
-        <v>1.006504336393452</v>
-      </c>
-      <c r="E7">
-        <v>1.40625</v>
-      </c>
-      <c r="F7">
-        <v>1.14891432916458</v>
-      </c>
-      <c r="G7">
-        <v>1.24712446586761</v>
-      </c>
-      <c r="H7">
-        <v>0.5235893847579874</v>
-      </c>
-      <c r="I7">
-        <v>0.4764106152420126</v>
-      </c>
-      <c r="J7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K7" t="s">
-        <v>22</v>
-      </c>
-      <c r="L7" t="s">
-        <v>23</v>
-      </c>
-      <c r="M7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="A8">
-        <v>2014</v>
-      </c>
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8">
-        <v>0.01536824324324321</v>
-      </c>
-      <c r="E8">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="F8">
-        <v>3.69459999331273</v>
-      </c>
-      <c r="G8">
-        <v>6.282988749273807</v>
-      </c>
-      <c r="H8">
-        <v>0.5705583655149382</v>
-      </c>
-      <c r="I8">
-        <v>0.4294416344850617</v>
-      </c>
-      <c r="J8" t="s">
-        <v>21</v>
-      </c>
-      <c r="K8" t="s">
-        <v>22</v>
-      </c>
-      <c r="L8" t="s">
-        <v>23</v>
-      </c>
-      <c r="M8" t="s">
-        <v>26</v>
-      </c>
-      <c r="N8">
-        <v>2.063735477916174</v>
-      </c>
-      <c r="O8">
-        <v>2.063735477916174</v>
-      </c>
-      <c r="P8">
+      <c r="N6">
+        <v>2.799367742338258</v>
+      </c>
+      <c r="O6">
+        <v>2.799367742338258</v>
+      </c>
+      <c r="P6">
         <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16">
-      <c r="A9">
-        <v>2014</v>
-      </c>
-      <c r="B9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9">
-        <v>6.071601107835621</v>
-      </c>
-      <c r="E9">
-        <v>6.65625</v>
-      </c>
-      <c r="F9">
-        <v>4.628669125976737</v>
-      </c>
-      <c r="G9">
-        <v>5.784804626044033</v>
-      </c>
-      <c r="H9">
-        <v>0.5203425664546144</v>
-      </c>
-      <c r="I9">
-        <v>0.4796574335453856</v>
-      </c>
-      <c r="J9" t="s">
-        <v>21</v>
-      </c>
-      <c r="K9" t="s">
-        <v>22</v>
-      </c>
-      <c r="L9" t="s">
-        <v>23</v>
-      </c>
-      <c r="M9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16">
-      <c r="A10">
-        <v>2014</v>
-      </c>
-      <c r="B10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10">
-        <v>0.7745227488775028</v>
-      </c>
-      <c r="E10">
-        <v>1.40625</v>
-      </c>
-      <c r="F10">
-        <v>1.023134447310966</v>
-      </c>
-      <c r="G10">
-        <v>1.187671637692011</v>
-      </c>
-      <c r="H10">
-        <v>0.5345658321696317</v>
-      </c>
-      <c r="I10">
-        <v>0.4654341678303684</v>
-      </c>
-      <c r="J10" t="s">
-        <v>22</v>
-      </c>
-      <c r="K10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L10" t="s">
-        <v>24</v>
-      </c>
-      <c r="M10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16">
-      <c r="A11">
-        <v>2018</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11">
-        <v>0.006999999999999978</v>
-      </c>
-      <c r="E11">
-        <v>6.533333333333332</v>
-      </c>
-      <c r="F11">
-        <v>4.139788819212143</v>
-      </c>
-      <c r="G11">
-        <v>5.291968212462604</v>
-      </c>
-      <c r="H11">
-        <v>0.5074764797709386</v>
-      </c>
-      <c r="I11">
-        <v>0.4925235202290613</v>
-      </c>
-      <c r="J11" t="s">
-        <v>22</v>
-      </c>
-      <c r="K11" t="s">
-        <v>22</v>
-      </c>
-      <c r="L11" t="s">
-        <v>24</v>
-      </c>
-      <c r="M11" t="s">
-        <v>26</v>
-      </c>
-      <c r="N11">
-        <v>2.578312672275927</v>
-      </c>
-      <c r="O11">
-        <v>2.578312672275927</v>
-      </c>
-      <c r="P11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16">
-      <c r="A12">
-        <v>2018</v>
-      </c>
-      <c r="B12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12">
-        <v>7.259981095064756</v>
-      </c>
-      <c r="E12">
-        <v>6.020833333333334</v>
-      </c>
-      <c r="F12">
-        <v>5.505856602954813</v>
-      </c>
-      <c r="G12">
-        <v>5.944073634095171</v>
-      </c>
-      <c r="H12">
-        <v>0.4955608090367326</v>
-      </c>
-      <c r="I12">
-        <v>0.5044391909632674</v>
-      </c>
-      <c r="J12" t="s">
-        <v>21</v>
-      </c>
-      <c r="K12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L12" t="s">
-        <v>25</v>
-      </c>
-      <c r="M12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16">
-      <c r="A13">
-        <v>2018</v>
-      </c>
-      <c r="B13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D13">
-        <v>1.30779306486022</v>
-      </c>
-      <c r="E13">
-        <v>1.229166666666667</v>
-      </c>
-      <c r="F13">
-        <v>1.137647266588851</v>
-      </c>
-      <c r="G13">
-        <v>1.151691393854048</v>
-      </c>
-      <c r="H13">
-        <v>0.5056822805017268</v>
-      </c>
-      <c r="I13">
-        <v>0.4943177194982732</v>
-      </c>
-      <c r="J13" t="s">
-        <v>22</v>
-      </c>
-      <c r="K13" t="s">
-        <v>22</v>
-      </c>
-      <c r="L13" t="s">
-        <v>25</v>
-      </c>
-      <c r="M13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16">
-      <c r="A14">
-        <v>2022</v>
-      </c>
-      <c r="B14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14">
-        <v>0.001374999999999932</v>
-      </c>
-      <c r="E14">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="F14">
-        <v>3.753336425842188</v>
-      </c>
-      <c r="G14">
-        <v>6.661208146972516</v>
-      </c>
-      <c r="H14">
-        <v>0.5677908010583421</v>
-      </c>
-      <c r="I14">
-        <v>0.4322091989416579</v>
-      </c>
-      <c r="J14" t="s">
-        <v>21</v>
-      </c>
-      <c r="K14" t="s">
-        <v>22</v>
-      </c>
-      <c r="L14" t="s">
-        <v>23</v>
-      </c>
-      <c r="M14" t="s">
-        <v>26</v>
-      </c>
-      <c r="N14">
-        <v>2.799367742338258</v>
-      </c>
-      <c r="O14">
-        <v>2.799367742338258</v>
-      </c>
-      <c r="P14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16">
-      <c r="A15">
-        <v>2022</v>
-      </c>
-      <c r="B15" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15">
-        <v>3.004590444317271</v>
-      </c>
-      <c r="E15">
-        <v>7.875</v>
-      </c>
-      <c r="F15">
-        <v>6.227766123397645</v>
-      </c>
-      <c r="G15">
-        <v>6.714528285451691</v>
-      </c>
-      <c r="H15">
-        <v>0.5232252085229694</v>
-      </c>
-      <c r="I15">
-        <v>0.4767747914770306</v>
-      </c>
-      <c r="J15" t="s">
-        <v>22</v>
-      </c>
-      <c r="K15" t="s">
-        <v>22</v>
-      </c>
-      <c r="L15" t="s">
-        <v>24</v>
-      </c>
-      <c r="M15" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16">
-      <c r="A16">
-        <v>2022</v>
-      </c>
-      <c r="B16" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16">
-        <v>1.141729553470553</v>
-      </c>
-      <c r="E16">
-        <v>1.458333333333333</v>
-      </c>
-      <c r="F16">
-        <v>0.998493356179856</v>
-      </c>
-      <c r="G16">
-        <v>1.162624750425286</v>
-      </c>
-      <c r="H16">
-        <v>0.5378164683009843</v>
-      </c>
-      <c r="I16">
-        <v>0.4621835316990157</v>
-      </c>
-      <c r="J16" t="s">
-        <v>21</v>
-      </c>
-      <c r="K16" t="s">
-        <v>22</v>
-      </c>
-      <c r="L16" t="s">
-        <v>23</v>
-      </c>
-      <c r="M16" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block2_National_Nested_Folds_v12.xlsx
+++ b/outputs/Block2_National_Nested_Folds_v12.xlsx
@@ -663,13 +663,13 @@
         <v>5.118421138250199</v>
       </c>
       <c r="G5">
-        <v>5.647888599724915</v>
+        <v>5.647888599724916</v>
       </c>
       <c r="H5">
         <v>0.4820351620929062</v>
       </c>
       <c r="I5">
-        <v>0.5179648379070939</v>
+        <v>0.5179648379070937</v>
       </c>
       <c r="J5" t="s">
         <v>18</v>

--- a/outputs/Block2_National_Nested_Folds_v12.xlsx
+++ b/outputs/Block2_National_Nested_Folds_v12.xlsx
@@ -663,13 +663,13 @@
         <v>5.118421138250199</v>
       </c>
       <c r="G5">
-        <v>5.647888599724916</v>
+        <v>5.647888599724915</v>
       </c>
       <c r="H5">
         <v>0.4820351620929062</v>
       </c>
       <c r="I5">
-        <v>0.5179648379070937</v>
+        <v>0.5179648379070939</v>
       </c>
       <c r="J5" t="s">
         <v>18</v>

--- a/outputs/Block2_National_Nested_Folds_v12.xlsx
+++ b/outputs/Block2_National_Nested_Folds_v12.xlsx
@@ -513,10 +513,10 @@
         <v>5.024892949502592</v>
       </c>
       <c r="G2">
-        <v>6.293341500897182</v>
+        <v>6.293341500897185</v>
       </c>
       <c r="H2">
-        <v>0.4795622463099145</v>
+        <v>0.4795622463099146</v>
       </c>
       <c r="I2">
         <v>0.5204377536900855</v>
@@ -563,10 +563,10 @@
         <v>5.511329271180229</v>
       </c>
       <c r="G3">
-        <v>6.000052338103545</v>
+        <v>6.000052338103547</v>
       </c>
       <c r="H3">
-        <v>0.5625189673269325</v>
+        <v>0.5625189673269324</v>
       </c>
       <c r="I3">
         <v>0.4374810326730675</v>
@@ -663,13 +663,13 @@
         <v>5.118421138250199</v>
       </c>
       <c r="G5">
-        <v>5.647888599724915</v>
+        <v>5.647888599724916</v>
       </c>
       <c r="H5">
         <v>0.4820351620929062</v>
       </c>
       <c r="I5">
-        <v>0.5179648379070939</v>
+        <v>0.5179648379070937</v>
       </c>
       <c r="J5" t="s">
         <v>18</v>

--- a/outputs/Block2_National_Nested_Folds_v12.xlsx
+++ b/outputs/Block2_National_Nested_Folds_v12.xlsx
@@ -513,10 +513,10 @@
         <v>5.024892949502592</v>
       </c>
       <c r="G2">
-        <v>6.293341500897185</v>
+        <v>6.293341500897182</v>
       </c>
       <c r="H2">
-        <v>0.4795622463099146</v>
+        <v>0.4795622463099145</v>
       </c>
       <c r="I2">
         <v>0.5204377536900855</v>
@@ -563,10 +563,10 @@
         <v>5.511329271180229</v>
       </c>
       <c r="G3">
-        <v>6.000052338103547</v>
+        <v>6.000052338103545</v>
       </c>
       <c r="H3">
-        <v>0.5625189673269324</v>
+        <v>0.5625189673269325</v>
       </c>
       <c r="I3">
         <v>0.4374810326730675</v>

--- a/outputs/Block2_National_Nested_Folds_v12.xlsx
+++ b/outputs/Block2_National_Nested_Folds_v12.xlsx
@@ -563,10 +563,10 @@
         <v>5.511329271180229</v>
       </c>
       <c r="G3">
-        <v>6.000052338103545</v>
+        <v>6.000052338103543</v>
       </c>
       <c r="H3">
-        <v>0.5625189673269325</v>
+        <v>0.5625189673269326</v>
       </c>
       <c r="I3">
         <v>0.4374810326730675</v>

--- a/outputs/Block2_National_Nested_Folds_v12.xlsx
+++ b/outputs/Block2_National_Nested_Folds_v12.xlsx
@@ -563,10 +563,10 @@
         <v>5.511329271180229</v>
       </c>
       <c r="G3">
-        <v>6.000052338103543</v>
+        <v>6.000052338103545</v>
       </c>
       <c r="H3">
-        <v>0.5625189673269326</v>
+        <v>0.5625189673269325</v>
       </c>
       <c r="I3">
         <v>0.4374810326730675</v>

--- a/outputs/Block2_National_Nested_Folds_v12.xlsx
+++ b/outputs/Block2_National_Nested_Folds_v12.xlsx
@@ -513,13 +513,13 @@
         <v>5.024892949502592</v>
       </c>
       <c r="G2">
-        <v>6.293341500897182</v>
+        <v>6.293341500897188</v>
       </c>
       <c r="H2">
         <v>0.4795622463099145</v>
       </c>
       <c r="I2">
-        <v>0.5204377536900855</v>
+        <v>0.5204377536900856</v>
       </c>
       <c r="J2" t="s">
         <v>18</v>
@@ -663,13 +663,13 @@
         <v>5.118421138250199</v>
       </c>
       <c r="G5">
-        <v>5.647888599724916</v>
+        <v>5.647888599724917</v>
       </c>
       <c r="H5">
-        <v>0.4820351620929062</v>
+        <v>0.482035162092906</v>
       </c>
       <c r="I5">
-        <v>0.5179648379070937</v>
+        <v>0.5179648379070941</v>
       </c>
       <c r="J5" t="s">
         <v>18</v>
@@ -713,13 +713,13 @@
         <v>6.513385977378117</v>
       </c>
       <c r="G6">
-        <v>6.165678152352301</v>
+        <v>6.165678152352303</v>
       </c>
       <c r="H6">
         <v>0.5964553373998983</v>
       </c>
       <c r="I6">
-        <v>0.4035446626001017</v>
+        <v>0.4035446626001016</v>
       </c>
       <c r="J6" t="s">
         <v>18</v>

--- a/outputs/Block2_National_Nested_Folds_v12.xlsx
+++ b/outputs/Block2_National_Nested_Folds_v12.xlsx
@@ -513,7 +513,7 @@
         <v>5.024892949502592</v>
       </c>
       <c r="G2">
-        <v>6.293341500897188</v>
+        <v>6.293341500897186</v>
       </c>
       <c r="H2">
         <v>0.4795622463099145</v>
@@ -563,13 +563,13 @@
         <v>5.511329271180229</v>
       </c>
       <c r="G3">
-        <v>6.000052338103545</v>
+        <v>6.000052338103544</v>
       </c>
       <c r="H3">
         <v>0.5625189673269325</v>
       </c>
       <c r="I3">
-        <v>0.4374810326730675</v>
+        <v>0.4374810326730676</v>
       </c>
       <c r="J3" t="s">
         <v>19</v>
@@ -613,13 +613,13 @@
         <v>4.938432989723164</v>
       </c>
       <c r="G4">
-        <v>5.199541323754511</v>
+        <v>5.199541323754512</v>
       </c>
       <c r="H4">
         <v>0.6207814507798668</v>
       </c>
       <c r="I4">
-        <v>0.3792185492201333</v>
+        <v>0.3792185492201332</v>
       </c>
       <c r="J4" t="s">
         <v>18</v>
@@ -663,13 +663,13 @@
         <v>5.118421138250199</v>
       </c>
       <c r="G5">
-        <v>5.647888599724917</v>
+        <v>5.647888599724916</v>
       </c>
       <c r="H5">
-        <v>0.482035162092906</v>
+        <v>0.4820351620929061</v>
       </c>
       <c r="I5">
-        <v>0.5179648379070941</v>
+        <v>0.517964837907094</v>
       </c>
       <c r="J5" t="s">
         <v>18</v>
@@ -713,10 +713,10 @@
         <v>6.513385977378117</v>
       </c>
       <c r="G6">
-        <v>6.165678152352303</v>
+        <v>6.165678152352301</v>
       </c>
       <c r="H6">
-        <v>0.5964553373998983</v>
+        <v>0.5964553373998984</v>
       </c>
       <c r="I6">
         <v>0.4035446626001016</v>

--- a/outputs/Block2_National_Nested_Folds_v12.xlsx
+++ b/outputs/Block2_National_Nested_Folds_v12.xlsx
@@ -513,13 +513,13 @@
         <v>5.024892949502592</v>
       </c>
       <c r="G2">
-        <v>6.293341500897186</v>
+        <v>6.293341500897182</v>
       </c>
       <c r="H2">
         <v>0.4795622463099145</v>
       </c>
       <c r="I2">
-        <v>0.5204377536900856</v>
+        <v>0.5204377536900855</v>
       </c>
       <c r="J2" t="s">
         <v>18</v>
@@ -563,13 +563,13 @@
         <v>5.511329271180229</v>
       </c>
       <c r="G3">
-        <v>6.000052338103544</v>
+        <v>6.000052338103545</v>
       </c>
       <c r="H3">
         <v>0.5625189673269325</v>
       </c>
       <c r="I3">
-        <v>0.4374810326730676</v>
+        <v>0.4374810326730675</v>
       </c>
       <c r="J3" t="s">
         <v>19</v>
@@ -613,13 +613,13 @@
         <v>4.938432989723164</v>
       </c>
       <c r="G4">
-        <v>5.199541323754512</v>
+        <v>5.199541323754511</v>
       </c>
       <c r="H4">
         <v>0.6207814507798668</v>
       </c>
       <c r="I4">
-        <v>0.3792185492201332</v>
+        <v>0.3792185492201333</v>
       </c>
       <c r="J4" t="s">
         <v>18</v>
@@ -663,13 +663,13 @@
         <v>5.118421138250199</v>
       </c>
       <c r="G5">
-        <v>5.647888599724916</v>
+        <v>5.647888599724915</v>
       </c>
       <c r="H5">
-        <v>0.4820351620929061</v>
+        <v>0.4820351620929062</v>
       </c>
       <c r="I5">
-        <v>0.517964837907094</v>
+        <v>0.5179648379070939</v>
       </c>
       <c r="J5" t="s">
         <v>18</v>
@@ -716,10 +716,10 @@
         <v>6.165678152352301</v>
       </c>
       <c r="H6">
-        <v>0.5964553373998984</v>
+        <v>0.5964553373998983</v>
       </c>
       <c r="I6">
-        <v>0.4035446626001016</v>
+        <v>0.4035446626001017</v>
       </c>
       <c r="J6" t="s">
         <v>18</v>

--- a/outputs/Block2_National_Nested_Folds_v12.xlsx
+++ b/outputs/Block2_National_Nested_Folds_v12.xlsx
@@ -713,13 +713,13 @@
         <v>6.513385977378117</v>
       </c>
       <c r="G6">
-        <v>6.165678152352301</v>
+        <v>6.165678152352304</v>
       </c>
       <c r="H6">
         <v>0.5964553373998983</v>
       </c>
       <c r="I6">
-        <v>0.4035446626001017</v>
+        <v>0.4035446626001016</v>
       </c>
       <c r="J6" t="s">
         <v>18</v>
